--- a/docs/Mapping_casi_uso/trascrizioni/Trascr_011.xlsx
+++ b/docs/Mapping_casi_uso/trascrizioni/Trascr_011.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="952" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="959" uniqueCount="162">
   <si>
     <t>Sezione</t>
   </si>
@@ -327,6 +327,12 @@
   </si>
   <si>
     <t>evento.intestatari[0]</t>
+  </si>
+  <si>
+    <t>Residenza al momento dell'evento originario</t>
+  </si>
+  <si>
+    <t>residenzaOriginaria</t>
   </si>
   <si>
     <t>Atto nascita intestatario</t>
@@ -550,7 +556,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H136"/>
+  <dimension ref="A1:H137"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.59765625" customWidth="true" bestFit="true"/>
@@ -3025,19 +3031,19 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B108" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="B108" s="2" t="s">
+      <c r="C108" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D108" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E108" s="2" t="s">
         <v>106</v>
-      </c>
-      <c r="C108" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D108" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="E108" s="2" t="s">
-        <v>108</v>
       </c>
       <c r="F108" s="2" t="s">
         <v>10</v>
@@ -3048,16 +3054,16 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B109" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D109" s="2" t="s">
         <v>109</v>
-      </c>
-      <c r="C109" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D109" s="2" t="s">
-        <v>107</v>
       </c>
       <c r="E109" s="2" t="s">
         <v>110</v>
@@ -3071,7 +3077,7 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B110" s="2" t="s">
         <v>111</v>
@@ -3080,7 +3086,7 @@
         <v>9</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E110" s="2" t="s">
         <v>112</v>
@@ -3094,7 +3100,7 @@
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B111" s="2" t="s">
         <v>113</v>
@@ -3103,7 +3109,7 @@
         <v>9</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E111" s="2" t="s">
         <v>114</v>
@@ -3117,7 +3123,7 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B112" s="2" t="s">
         <v>115</v>
@@ -3126,7 +3132,7 @@
         <v>9</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E112" s="2" t="s">
         <v>116</v>
@@ -3140,7 +3146,7 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B113" s="2" t="s">
         <v>117</v>
@@ -3149,7 +3155,7 @@
         <v>9</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E113" s="2" t="s">
         <v>118</v>
@@ -3163,7 +3169,7 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B114" s="2" t="s">
         <v>119</v>
@@ -3172,10 +3178,10 @@
         <v>9</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>25</v>
+        <v>120</v>
       </c>
       <c r="F114" s="2" t="s">
         <v>10</v>
@@ -3186,19 +3192,19 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>121</v>
+        <v>25</v>
       </c>
       <c r="F115" s="2" t="s">
         <v>10</v>
@@ -3209,7 +3215,7 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B116" s="2" t="s">
         <v>122</v>
@@ -3218,10 +3224,10 @@
         <v>9</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>28</v>
+        <v>123</v>
       </c>
       <c r="F116" s="2" t="s">
         <v>10</v>
@@ -3232,19 +3238,19 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>124</v>
+        <v>28</v>
       </c>
       <c r="F117" s="2" t="s">
         <v>10</v>
@@ -3255,7 +3261,7 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B118" s="2" t="s">
         <v>125</v>
@@ -3264,7 +3270,7 @@
         <v>16</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E118" s="2" t="s">
         <v>126</v>
@@ -3278,7 +3284,7 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B119" s="2" t="s">
         <v>127</v>
@@ -3287,7 +3293,7 @@
         <v>16</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E119" s="2" t="s">
         <v>128</v>
@@ -3301,16 +3307,16 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B120" s="2" t="s">
         <v>129</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E120" s="2" t="s">
         <v>130</v>
@@ -3324,19 +3330,19 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B121" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="B121" s="2" t="s">
+      <c r="C121" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D121" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E121" s="2" t="s">
         <v>132</v>
-      </c>
-      <c r="C121" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D121" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="E121" s="2" t="s">
-        <v>134</v>
       </c>
       <c r="F121" s="2" t="s">
         <v>10</v>
@@ -3347,16 +3353,16 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B122" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C122" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D122" s="2" t="s">
         <v>135</v>
-      </c>
-      <c r="C122" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D122" s="2" t="s">
-        <v>133</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>136</v>
@@ -3370,7 +3376,7 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B123" s="2" t="s">
         <v>137</v>
@@ -3379,7 +3385,7 @@
         <v>9</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E123" s="2" t="s">
         <v>138</v>
@@ -3393,19 +3399,19 @@
     </row>
     <row r="124">
       <c r="A124" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>63</v>
+        <v>139</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F124" s="2" t="s">
         <v>10</v>
@@ -3416,16 +3422,16 @@
     </row>
     <row r="125">
       <c r="A125" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>140</v>
+        <v>63</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E125" s="2" t="s">
         <v>141</v>
@@ -3439,16 +3445,16 @@
     </row>
     <row r="126">
       <c r="A126" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B126" s="2" t="s">
         <v>142</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E126" s="2" t="s">
         <v>143</v>
@@ -3462,7 +3468,7 @@
     </row>
     <row r="127">
       <c r="A127" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B127" s="2" t="s">
         <v>144</v>
@@ -3471,7 +3477,7 @@
         <v>16</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E127" s="2" t="s">
         <v>145</v>
@@ -3485,19 +3491,19 @@
     </row>
     <row r="128">
       <c r="A128" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B128" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="B128" s="2" t="s">
-        <v>132</v>
-      </c>
       <c r="C128" s="2" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D128" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="E128" s="2" t="s">
         <v>147</v>
-      </c>
-      <c r="E128" s="2" t="s">
-        <v>134</v>
       </c>
       <c r="F128" s="2" t="s">
         <v>10</v>
@@ -3508,16 +3514,16 @@
     </row>
     <row r="129">
       <c r="A129" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E129" s="2" t="s">
         <v>136</v>
@@ -3531,7 +3537,7 @@
     </row>
     <row r="130">
       <c r="A130" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B130" s="2" t="s">
         <v>137</v>
@@ -3540,7 +3546,7 @@
         <v>9</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E130" s="2" t="s">
         <v>138</v>
@@ -3554,19 +3560,19 @@
     </row>
     <row r="131">
       <c r="A131" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="F131" s="2" t="s">
         <v>10</v>
@@ -3577,7 +3583,7 @@
     </row>
     <row r="132">
       <c r="A132" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B132" s="2" t="s">
         <v>150</v>
@@ -3586,7 +3592,7 @@
         <v>16</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E132" s="2" t="s">
         <v>151</v>
@@ -3600,7 +3606,7 @@
     </row>
     <row r="133">
       <c r="A133" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B133" s="2" t="s">
         <v>152</v>
@@ -3609,7 +3615,7 @@
         <v>16</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E133" s="2" t="s">
         <v>153</v>
@@ -3623,7 +3629,7 @@
     </row>
     <row r="134">
       <c r="A134" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B134" s="2" t="s">
         <v>154</v>
@@ -3632,7 +3638,7 @@
         <v>16</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E134" s="2" t="s">
         <v>155</v>
@@ -3646,7 +3652,7 @@
     </row>
     <row r="135">
       <c r="A135" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B135" s="2" t="s">
         <v>156</v>
@@ -3655,7 +3661,7 @@
         <v>16</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E135" s="2" t="s">
         <v>157</v>
@@ -3669,7 +3675,7 @@
     </row>
     <row r="136">
       <c r="A136" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B136" s="2" t="s">
         <v>158</v>
@@ -3678,7 +3684,7 @@
         <v>16</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E136" s="2" t="s">
         <v>159</v>
@@ -3687,6 +3693,29 @@
         <v>10</v>
       </c>
       <c r="G136" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B137" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C137" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D137" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E137" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="F137" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G137" s="2" t="s">
         <v>26</v>
       </c>
     </row>
